--- a/docs/创新药_第一阶段_v2_claude.xlsx
+++ b/docs/创新药_第一阶段_v2_claude.xlsx
@@ -10,10 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第一阶段" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第一阶段-指标计算口径" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第二阶段" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第三阶段" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="时间线" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径字典" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="159567成分股" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第二阶段-指标计算口径" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第三阶段" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="时间线" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径字典" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="159567成分股" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -999,7 +1000,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1214,6 +1215,12 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3864,6 +3871,657 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.3308823529412" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <cols>
+    <col width="24" customWidth="1" style="3" min="1" max="1"/>
+    <col width="24" customWidth="1" style="1" min="2" max="4"/>
+    <col width="24" customWidth="1" style="1" min="5" max="5"/>
+    <col width="42" customWidth="1" style="1" min="6" max="6"/>
+    <col width="14.7132352941176" customWidth="1" style="1" min="7" max="7"/>
+    <col width="10.5735294117647" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18" customWidth="1" style="1" min="9" max="11"/>
+    <col width="10.5735294117647" customWidth="1" style="1" min="12" max="12"/>
+    <col width="42" customWidth="1" style="1" min="13" max="14"/>
+    <col width="42" customWidth="1" style="1" min="14" max="14"/>
+    <col width="18" customWidth="1" style="1" min="15" max="15"/>
+    <col width="42" customWidth="1" style="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B1" s="29" t="inlineStr">
+        <is>
+          <t>指标编号</t>
+        </is>
+      </c>
+      <c r="C1" s="29" t="inlineStr">
+        <is>
+          <t>指标大类</t>
+        </is>
+      </c>
+      <c r="D1" s="29" t="inlineStr">
+        <is>
+          <t>指标名称</t>
+        </is>
+      </c>
+      <c r="E1" s="29" t="inlineStr">
+        <is>
+          <t>量化口径</t>
+        </is>
+      </c>
+      <c r="F1" s="29" t="inlineStr">
+        <is>
+          <t>计算口径说明</t>
+        </is>
+      </c>
+      <c r="G1" s="29" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="H1" s="29" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="I1" s="29" t="inlineStr">
+        <is>
+          <t>超预期条件</t>
+        </is>
+      </c>
+      <c r="J1" s="29" t="inlineStr">
+        <is>
+          <t>符合预期条件</t>
+        </is>
+      </c>
+      <c r="K1" s="29" t="inlineStr">
+        <is>
+          <t>低于预期条件</t>
+        </is>
+      </c>
+      <c r="L1" s="30" t="inlineStr">
+        <is>
+          <t>建议权重</t>
+        </is>
+      </c>
+      <c r="M1" s="29" t="inlineStr">
+        <is>
+          <t>计算示例</t>
+        </is>
+      </c>
+      <c r="N1" s="29" t="inlineStr">
+        <is>
+          <t>数据来源建议</t>
+        </is>
+      </c>
+      <c r="O1" s="29" t="inlineStr">
+        <is>
+          <t>实际值（留空）</t>
+        </is>
+      </c>
+      <c r="P1" s="29" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="420" customHeight="1" s="1">
+      <c r="A2" s="75" t="inlineStr">
+        <is>
+          <t>第二阶段：产业验证</t>
+        </is>
+      </c>
+      <c r="B2" s="75" t="inlineStr">
+        <is>
+          <t>S2-01</t>
+        </is>
+      </c>
+      <c r="C2" s="75" t="inlineStr">
+        <is>
+          <t>BD</t>
+        </is>
+      </c>
+      <c r="D2" s="75" t="inlineStr">
+        <is>
+          <t>BD落地频率</t>
+        </is>
+      </c>
+      <c r="E2" s="75" t="inlineStr">
+        <is>
+          <t>近90日重大BD笔数 ÷ 前4个完整90日窗口重大BD笔数均值</t>
+        </is>
+      </c>
+      <c r="F2" s="75" t="inlineStr">
+        <is>
+          <t>由智能体联网检索并结构化记录重大BD事件，代码按事件日期统计。当前观察窗为最近90日；历史基准必须使用当前观察窗之前的前4个完整90日窗口，避免把当前事件同时计入分子和基准。重大BD口径全年保持一致：优先纳入明确披露的license-out、全球/海外权益合作、战略级合作；建议满足首付款≥5000万美元、总交易额≥5亿美元、临床阶段核心资产海外权益授权、或公司/交易所明确披露为重大合作之一。每条事件记录入库理由和可靠来源。</t>
+        </is>
+      </c>
+      <c r="G2" s="75" t="inlineStr">
+        <is>
+          <t>倍</t>
+        </is>
+      </c>
+      <c r="H2" s="75" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I2" s="75" t="inlineStr">
+        <is>
+          <t>≥1.5x</t>
+        </is>
+      </c>
+      <c r="J2" s="75" t="inlineStr">
+        <is>
+          <t>0.8x–1.5x</t>
+        </is>
+      </c>
+      <c r="K2" s="75" t="inlineStr">
+        <is>
+          <t>&lt;0.8x</t>
+        </is>
+      </c>
+      <c r="L2" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M2" s="75" t="inlineStr">
+        <is>
+          <t>deals_90d = count(BD, T-89 ~ T)；baseline = mean(count(BD, T-179 ~ T-90), count(BD, T-269 ~ T-180), count(BD, T-359 ~ T-270), count(BD, T-449 ~ T-360))；bd_frequency = deals_90d / baseline</t>
+        </is>
+      </c>
+      <c r="N2" s="75" t="inlineStr">
+        <is>
+          <t>智能体采集：公司官网新闻稿、交易所公告、合作方官网、权威财经媒体。
+结构化字段：date、company、ticker、asset、partner、upfront_usd、near_term_milestone_usd、total_value_usd、rights_scope、materiality_reason、source_url、source_tier、status。
+本地事件库：s2/data/bd_events.csv。</t>
+        </is>
+      </c>
+      <c r="O2" s="75" t="n"/>
+      <c r="P2" s="75" t="inlineStr">
+        <is>
+          <t>历史基准不足时，正式值写“数据缺失”；同时展示近90日重大BD笔数作为辅助观察值，不得因样本少直接给满分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="420" customHeight="1" s="1">
+      <c r="A3" s="75" t="inlineStr">
+        <is>
+          <t>第二阶段：产业验证</t>
+        </is>
+      </c>
+      <c r="B3" s="75" t="inlineStr">
+        <is>
+          <t>S2-02</t>
+        </is>
+      </c>
+      <c r="C3" s="75" t="inlineStr">
+        <is>
+          <t>BD</t>
+        </is>
+      </c>
+      <c r="D3" s="75" t="inlineStr">
+        <is>
+          <t>BD金额质量</t>
+        </is>
+      </c>
+      <c r="E3" s="75" t="inlineStr">
+        <is>
+          <t>近90日BD首付款+近期里程碑金额 ÷ 去年同期金额</t>
+        </is>
+      </c>
+      <c r="F3" s="75" t="inlineStr">
+        <is>
+          <t>由智能体从可靠来源提取BD金额。正式主值使用已明确披露的首付款（upfront）与近期里程碑（near-term milestones）之和，并与去年同期90日窗口比较。另行沉淀质量金额用于辅助观察：quality_amount = upfront + 0.5 × near_term_milestone + 0.1 × long_term_milestone。总交易额仅作为事件重要性参考，不直接等同于高质量可兑现现金流。</t>
+        </is>
+      </c>
+      <c r="G3" s="75" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H3" s="75" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I3" s="75" t="inlineStr">
+        <is>
+          <t>≥150%</t>
+        </is>
+      </c>
+      <c r="J3" s="75" t="inlineStr">
+        <is>
+          <t>80%–150%</t>
+        </is>
+      </c>
+      <c r="K3" s="75" t="inlineStr">
+        <is>
+          <t>&lt;80%</t>
+        </is>
+      </c>
+      <c r="L3" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M3" s="75" t="inlineStr">
+        <is>
+          <t>amount_90d = Σ(upfront + near_term_milestone, T-89 ~ T)；amount_yoy = Σ(upfront + near_term_milestone, T-454 ~ T-365)；bd_quality_yoy = amount_90d / amount_yoy；quality_amount_90d = Σ(upfront + 0.5×near_term + 0.1×long_term)</t>
+        </is>
+      </c>
+      <c r="N3" s="75" t="inlineStr">
+        <is>
+          <t>智能体采集：公司官网、合作方官网、交易所公告、路透等权威来源。
+结构化字段：upfront_usd、near_term_milestone_usd、long_term_milestone_usd、total_value_usd、rights_scope、source_url。
+本地事件库：s2/data/bd_events.csv。</t>
+        </is>
+      </c>
+      <c r="O3" s="75" t="n"/>
+      <c r="P3" s="75" t="inlineStr">
+        <is>
+          <t>去年同期金额缺失时，正式同比值写“数据缺失”；可展示近90日raw金额和quality_amount，但不得使用绝对金额直接替代正式同比评级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="420" customHeight="1" s="1">
+      <c r="A4" s="75" t="inlineStr">
+        <is>
+          <t>第二阶段：产业验证</t>
+        </is>
+      </c>
+      <c r="B4" s="75" t="inlineStr">
+        <is>
+          <t>S2-03</t>
+        </is>
+      </c>
+      <c r="C4" s="75" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
+      <c r="D4" s="75" t="inlineStr">
+        <is>
+          <t>龙头业绩兑现率</t>
+        </is>
+      </c>
+      <c r="E4" s="75" t="inlineStr">
+        <is>
+          <t>已披露且有一致预期的核心龙头中，营收或利润至少一项超一致预期的公司占比</t>
+        </is>
+      </c>
+      <c r="F4" s="75" t="inlineStr">
+        <is>
+          <t>核心龙头样本池固定，并仅在正式调整时统一更新。智能体负责检索财报、业绩公告和可靠的一致预期来源，代码根据实际值与一致预期值判断是否beat。单家公司在同一报告期只计一次。若只有同比增速、没有一致预期，不应主观标记为超预期，可作为辅助信息展示。</t>
+        </is>
+      </c>
+      <c r="G4" s="75" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H4" s="75" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I4" s="75" t="inlineStr">
+        <is>
+          <t>≥60%</t>
+        </is>
+      </c>
+      <c r="J4" s="75" t="inlineStr">
+        <is>
+          <t>40%–60%</t>
+        </is>
+      </c>
+      <c r="K4" s="75" t="inlineStr">
+        <is>
+          <t>&lt;40%</t>
+        </is>
+      </c>
+      <c r="L4" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M4" s="75" t="inlineStr">
+        <is>
+          <t>beat_i = (revenue_actual_i &gt; revenue_consensus_i) OR (profit_actual_i &gt; profit_consensus_i)；earnings_conversion = count(beat_i = true) / count(reported leaders with consensus)</t>
+        </is>
+      </c>
+      <c r="N4" s="75" t="inlineStr">
+        <is>
+          <t>智能体采集：公司财报、交易所公告、公司业绩会材料、可靠一致预期数据库或权威媒体。
+建议固定核心龙头池：石药集团、百济神州、康方生物、中国生物制药、信达生物；如需扩展，记录生效日期。
+结构化字段：period、revenue_actual、revenue_consensus、profit_actual、profit_consensus、consensus_source_url、source_url。
+本地事件库：s2/data/earnings_events.csv。</t>
+        </is>
+      </c>
+      <c r="O4" s="75" t="n"/>
+      <c r="P4" s="75" t="inlineStr">
+        <is>
+          <t>缺少一致预期时，正式样本数不增加，写“数据缺失”；同比增长、扭亏或产品销售放量可进入当天简报，但不能替代beat判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="420" customHeight="1" s="1">
+      <c r="A5" s="75" t="inlineStr">
+        <is>
+          <t>第二阶段：产业验证</t>
+        </is>
+      </c>
+      <c r="B5" s="75" t="inlineStr">
+        <is>
+          <t>S2-04</t>
+        </is>
+      </c>
+      <c r="C5" s="75" t="inlineStr">
+        <is>
+          <t>数据</t>
+        </is>
+      </c>
+      <c r="D5" s="75" t="inlineStr">
+        <is>
+          <t>数据催化转化率</t>
+        </is>
+      </c>
+      <c r="E5" s="75" t="inlineStr">
+        <is>
+          <t>AACR/ASCO/ESMO等重点临床事件后5个完整交易日，跑赢主题ETF的重点标的占比</t>
+        </is>
+      </c>
+      <c r="F5" s="75" t="inlineStr">
+        <is>
+          <t>智能体负责筛选重点临床事件并记录实际披露时间。纳入范围建议限定为：注册性或关键Phase II/III数据、OS/PFS/ORR等核心终点正式披露、重要会议plenary/oral/late-breaking数据、可支持NDA/BLA的正式结果。代码以effective_trade_date为起点，严格等待5个完整交易日后一次性计算，不使用第1–4日部分窗口。预告与正式结果通过related_event_id关联，避免同一催化重复计分。</t>
+        </is>
+      </c>
+      <c r="G5" s="75" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H5" s="75" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I5" s="75" t="inlineStr">
+        <is>
+          <t>≥60%</t>
+        </is>
+      </c>
+      <c r="J5" s="75" t="inlineStr">
+        <is>
+          <t>40%–60%</t>
+        </is>
+      </c>
+      <c r="K5" s="75" t="inlineStr">
+        <is>
+          <t>&lt;40%</t>
+        </is>
+      </c>
+      <c r="L5" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M5" s="75" t="inlineStr">
+        <is>
+          <t>stock_ret_5d = close_stock(D5) / close_stock(D0) - 1；etf_ret_5d = close_589720(D5) / close_589720(D0) - 1；clinical_conversion = count(stock_ret_5d &gt; etf_ret_5d) / count(matured events with stock prices)</t>
+        </is>
+      </c>
+      <c r="N5" s="75" t="inlineStr">
+        <is>
+          <t>智能体采集：公司官网、交易所公告、FDA/NMPA、ClinicalTrials.gov、会议官网、PRNewswire、GlobeNewswire。
+结构化字段：published_at、effective_trade_date、company、ticker、conference、asset、phase、data_type、data_judgement、related_event_id、source_url、status。
+本地行情：标的日线 + 589720日线。
+本地事件库：s2/data/clinical_events.csv。</t>
+        </is>
+      </c>
+      <c r="O5" s="75" t="n"/>
+      <c r="P5" s="75" t="inlineStr">
+        <is>
+          <t>标的行情缺失时，ETF跑赢159557可作为proxy_value单独展示，但不得混入正式clinical_conversion。未满5个交易日的事件标记pending；当日没有新增成熟样本时沿用最近有效观测，并注明沿用日期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="420" customHeight="1" s="1">
+      <c r="A6" s="75" t="inlineStr">
+        <is>
+          <t>第二阶段：产业验证</t>
+        </is>
+      </c>
+      <c r="B6" s="75" t="inlineStr">
+        <is>
+          <t>S2-05</t>
+        </is>
+      </c>
+      <c r="C6" s="75" t="inlineStr">
+        <is>
+          <t>龙头</t>
+        </is>
+      </c>
+      <c r="D6" s="75" t="inlineStr">
+        <is>
+          <t>龙头接力强度</t>
+        </is>
+      </c>
+      <c r="E6" s="75" t="inlineStr">
+        <is>
+          <t>核心催化后5个完整交易日，本地A股龙头池相对589720的超额收益中位数</t>
+        </is>
+      </c>
+      <c r="F6" s="75" t="inlineStr">
+        <is>
+          <t>核心催化包括重大BD、重点临床数据和重大审批。智能体负责确认催化是否达到入库标准；代码计算固定本地A股龙头池在催化窗口内相对589720的5日超额收益，并取中位数。正式池仅使用本地行情可稳定复现的A股龙头：百济神州（688235.SH）、艾力斯（688578.SH）、百利天恒（688506.SH）、君实生物（688180.SH）、泽璟制药（688266.SH）。港股龙头池独立列入观察层，不混入正式得分。</t>
+        </is>
+      </c>
+      <c r="G6" s="75" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H6" s="75" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I6" s="75" t="inlineStr">
+        <is>
+          <t>≥5%</t>
+        </is>
+      </c>
+      <c r="J6" s="75" t="inlineStr">
+        <is>
+          <t>0%–5%</t>
+        </is>
+      </c>
+      <c r="K6" s="75" t="inlineStr">
+        <is>
+          <t>&lt;0%</t>
+        </is>
+      </c>
+      <c r="L6" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M6" s="75" t="inlineStr">
+        <is>
+          <t>leader_excess_event = median(ret_5d_local_a_leader_i - ret_5d_589720, fixed_local_a_leader_pool)；leader_relay_strength = median(leader_excess_event, matured core catalyst events)</t>
+        </is>
+      </c>
+      <c r="N6" s="75" t="inlineStr">
+        <is>
+          <t>智能体采集：重大BD、重点临床、重大审批事件及可靠来源。
+正式行情：s2/data/leader_pool.csv中的固定本地A股龙头池日线 + 589720日线。
+观察行情：s2/data/hk_observation_pool.csv中的港股龙头池，如本地港股行情缺失则明确写“数据缺失”。
+本地事件库：s2/data/bd_events.csv、clinical_events.csv、regulatory_events.csv。</t>
+        </is>
+      </c>
+      <c r="O6" s="75" t="n"/>
+      <c r="P6" s="75" t="inlineStr">
+        <is>
+          <t>严格等待5个完整交易日。港股观察值不参与正式主值。无新增成熟样本时最多沿用最近有效观测20个交易日，并注明待验证事件数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="300" customHeight="1" s="1">
+      <c r="A7" s="75" t="inlineStr">
+        <is>
+          <t>第二阶段：产业验证</t>
+        </is>
+      </c>
+      <c r="B7" s="75" t="inlineStr">
+        <is>
+          <t>共用规则</t>
+        </is>
+      </c>
+      <c r="C7" s="75" t="inlineStr">
+        <is>
+          <t>智能体边界</t>
+        </is>
+      </c>
+      <c r="D7" s="75" t="inlineStr">
+        <is>
+          <t>事件采集与结构化</t>
+        </is>
+      </c>
+      <c r="E7" s="75" t="inlineStr">
+        <is>
+          <t>智能体负责联网探索、可靠来源核实、字段提取和入库，不允许临场主观重打分</t>
+        </is>
+      </c>
+      <c r="F7" s="75" t="inlineStr">
+        <is>
+          <t>智能体可以判断事件是否符合固定入库标准，并记录materiality_reason、source_url和source_tier；所有raw_score、adjusted_score、等级和趋势变化必须由本地代码根据固定公式生成。新增事件必须去重，稳定event_id推荐由event_type + company + asset/period/approval_type + partner + date生成；新增可靠来源归并到source_urls，并记录discovered_at。</t>
+        </is>
+      </c>
+      <c r="G7" s="75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="76" t="n"/>
+      <c r="M7" s="75" t="inlineStr">
+        <is>
+          <t>事件事实 -&gt; 结构化CSV -&gt; 本地公式计算 -&gt; 置信度调整 -&gt; 指标日报 -&gt; 当天情况简报</t>
+        </is>
+      </c>
+      <c r="N7" s="75" t="inlineStr">
+        <is>
+          <t>优先来源：公司官网、交易所公告、FDA/NMPA、ClinicalTrials.gov、会议官网；其次为PRNewswire、GlobeNewswire和权威财经媒体。禁止无来源传闻和媒体猜测。</t>
+        </is>
+      </c>
+      <c r="O7" s="75" t="n"/>
+      <c r="P7" s="75" t="inlineStr">
+        <is>
+          <t>事件库字段包括event_id、discovered_at、published_at、effective_trade_date、materiality_reason、related_event_id、verification_status、market_validation_status和source_urls。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="300" customHeight="1" s="1">
+      <c r="A8" s="75" t="inlineStr">
+        <is>
+          <t>第二阶段：产业验证</t>
+        </is>
+      </c>
+      <c r="B8" s="75" t="inlineStr">
+        <is>
+          <t>共用规则</t>
+        </is>
+      </c>
+      <c r="C8" s="75" t="inlineStr">
+        <is>
+          <t>数据质量</t>
+        </is>
+      </c>
+      <c r="D8" s="75" t="inlineStr">
+        <is>
+          <t>缺失、替代与置信度</t>
+        </is>
+      </c>
+      <c r="E8" s="75" t="inlineStr">
+        <is>
+          <t>正式值、替代值、缺失项和待验证状态分层展示</t>
+        </is>
+      </c>
+      <c r="F8" s="75" t="inlineStr">
+        <is>
+          <t>raw_score保留为原始评分；正式结果使用adjusted_score。事件样本数&lt;3时单项adjusted_score上限0.65；样本数&lt;5时上限0.75。替代口径必须单独展示，不与正式主值混算。去年同期基准缺失、一致预期缺失、真实标的行情缺失时明确写“数据缺失”。未满规定交易窗口时标记pending，不得按0分处理。无新增成熟样本时，最近有效观测最多沿用20个交易日。</t>
+        </is>
+      </c>
+      <c r="G8" s="75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="76" t="n"/>
+      <c r="M8" s="75" t="inlineStr">
+        <is>
+          <t>official_value = formal_metric_or_missing；proxy_value = auxiliary_metric；adjusted_score = confidence_cap(raw_score, sample_count, missing_data, proxy_usage)</t>
+        </is>
+      </c>
+      <c r="N8" s="75" t="inlineStr">
+        <is>
+          <t>输出建议：s2/output/s2_daily_report.md保留指标历史台账；s2/output/daily_brief.md记录当天新增事件、成熟样本、待验证样本和客观变化。</t>
+        </is>
+      </c>
+      <c r="O8" s="75" t="n"/>
+      <c r="P8" s="75" t="inlineStr">
+        <is>
+          <t>S1与S2分别展示，不机械叠加；S1作为市场预期与资金承接背景，S2作为产业验证状态。不得自动输出持仓或交易动作。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.3308823529412" defaultRowHeight="15.2"/>
   <cols>
@@ -4413,7 +5071,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4893,7 +5551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5070,7 +5728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5082,7 +5740,7 @@
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
         <is>
-          <t>589720（港股创新药ETF）成分股列表</t>
+          <t>159567.SZ（港股创新药ETF）成分股列表</t>
         </is>
       </c>
     </row>
